--- a/スケジュール管理.xlsx
+++ b/スケジュール管理.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ooharastudent-my.sharepoint.com/personal/fko2647063_stu_o-hara_ac_jp/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HigutiHaruyuki\Documents\GitHub\Fugedaku_TeamKagoshima\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="11_31802F1733C7A0836B02CE998F682C9D7A7B838F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0C3D7C0-EA1B-4AAF-B6A0-90103C42CB4F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61348859-246A-4F85-AACA-40C6E65CB8D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>制作スケジュール</t>
   </si>
@@ -119,6 +119,10 @@
   </si>
   <si>
     <t>ｊ</t>
+  </si>
+  <si>
+    <t>test</t>
+    <phoneticPr fontId="7"/>
   </si>
 </sst>
 </file>
@@ -179,6 +183,8 @@
       <sz val="16"/>
       <color rgb="FFFF0000"/>
       <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -843,10 +849,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1146,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:16" ht="25.5" x14ac:dyDescent="0.4">
@@ -1802,6 +1804,11 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
     </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="L20" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
